--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -43,63 +43,63 @@
     <t>P1</t>
   </si>
   <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>TC_MOB_AUTH_002</t>
+  </si>
+  <si>
+    <t>Verify login validation error when password is empty</t>
+  </si>
+  <si>
+    <t>TC_MOB_AUTH_003</t>
+  </si>
+  <si>
+    <t>Verify biometric / fingerprint authentication prompt</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
     <t>0.03</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>TC_MOB_AUTH_002</t>
-  </si>
-  <si>
-    <t>Verify login validation error when password is empty</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>TC_MOB_AUTH_003</t>
-  </si>
-  <si>
-    <t>Verify biometric / fingerprint authentication prompt</t>
-  </si>
-  <si>
-    <t>P2</t>
+    <t>TC_MOB_AUTH_004</t>
+  </si>
+  <si>
+    <t>Verify Google Sign-In native intent launch</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>TC_MOB_AUTH_005</t>
+  </si>
+  <si>
+    <t>Verify OTP autofill via Android SMS Retriever API</t>
   </si>
   <si>
     <t>0.05</t>
   </si>
   <si>
-    <t>TC_MOB_AUTH_004</t>
-  </si>
-  <si>
-    <t>Verify Google Sign-In native intent launch</t>
-  </si>
-  <si>
-    <t>P3</t>
+    <t>TC_MOB_AUTH_006</t>
+  </si>
+  <si>
+    <t>Verify account logout clears SecureStore tokens</t>
+  </si>
+  <si>
+    <t>TC_MOB_AUTH_007</t>
+  </si>
+  <si>
+    <t>Verify user login on Android with valid email and password (Variation 2 - Mobile Edge Test)</t>
   </si>
   <si>
     <t>0.02</t>
   </si>
   <si>
-    <t>TC_MOB_AUTH_005</t>
-  </si>
-  <si>
-    <t>Verify OTP autofill via Android SMS Retriever API</t>
-  </si>
-  <si>
-    <t>TC_MOB_AUTH_006</t>
-  </si>
-  <si>
-    <t>Verify account logout clears SecureStore tokens</t>
-  </si>
-  <si>
-    <t>TC_MOB_AUTH_007</t>
-  </si>
-  <si>
-    <t>Verify user login on Android with valid email and password (Variation 2 - Mobile Edge Test)</t>
-  </si>
-  <si>
     <t>TC_MOB_AUTH_008</t>
   </si>
   <si>
@@ -136,6 +136,9 @@
     <t>Verify user login on Android with valid email and password (Variation 3 - Mobile Edge Test)</t>
   </si>
   <si>
+    <t>0.01</t>
+  </si>
+  <si>
     <t>TC_MOB_AUTH_014</t>
   </si>
   <si>
@@ -671,9 +674,6 @@
   </si>
   <si>
     <t>Verify downloading digital blood donor certificate (PDF) (Variation 4 - Mobile Edge Test)</t>
-  </si>
-  <si>
-    <t>0.01</t>
   </si>
   <si>
     <t>TC_MOB_PROF_012</t>
@@ -3682,7 +3682,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -3690,19 +3690,19 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -3710,19 +3710,19 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -3730,19 +3730,19 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -3750,19 +3750,19 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -3770,19 +3770,19 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
@@ -3799,10 +3799,10 @@
         <v>30</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -3822,7 +3822,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -3842,7 +3842,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -3859,10 +3859,10 @@
         <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -3879,10 +3879,10 @@
         <v>38</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -3902,7 +3902,7 @@
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -3910,19 +3910,19 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -3930,19 +3930,19 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
@@ -3950,19 +3950,19 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -3970,19 +3970,19 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -3990,19 +3990,19 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -4010,19 +4010,19 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>11</v>
@@ -4030,19 +4030,19 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -4050,13 +4050,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>9</v>
@@ -4070,19 +4070,19 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -4090,19 +4090,19 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>11</v>
@@ -4110,16 +4110,16 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>10</v>
@@ -4130,19 +4130,19 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>11</v>
@@ -4150,19 +4150,19 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -4170,19 +4170,19 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -4190,19 +4190,19 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -4210,19 +4210,19 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>11</v>
@@ -4230,19 +4230,19 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -4250,19 +4250,19 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>11</v>
@@ -4270,19 +4270,19 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -4290,19 +4290,19 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
@@ -4310,19 +4310,19 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -4330,19 +4330,19 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>11</v>
@@ -4350,19 +4350,19 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>11</v>
@@ -4370,19 +4370,19 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>11</v>
@@ -4390,19 +4390,19 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>11</v>
@@ -4410,19 +4410,19 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>11</v>
@@ -4430,19 +4430,19 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>11</v>
@@ -4450,19 +4450,19 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -4470,19 +4470,19 @@
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>11</v>
@@ -4490,16 +4490,16 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>10</v>
@@ -4510,19 +4510,19 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -4530,19 +4530,19 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -4550,19 +4550,19 @@
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -4570,19 +4570,19 @@
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -4590,19 +4590,19 @@
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -4610,19 +4610,19 @@
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -4630,19 +4630,19 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>11</v>
@@ -4650,19 +4650,19 @@
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>11</v>
@@ -4670,19 +4670,19 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>11</v>
@@ -4690,19 +4690,19 @@
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>11</v>
@@ -4710,19 +4710,19 @@
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -4730,19 +4730,19 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>11</v>
@@ -4750,16 +4750,16 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>10</v>
@@ -4770,19 +4770,19 @@
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -4790,19 +4790,19 @@
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
@@ -4810,19 +4810,19 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>11</v>
@@ -4830,16 +4830,16 @@
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>10</v>
@@ -4850,13 +4850,13 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>9</v>
@@ -4870,19 +4870,19 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>11</v>
@@ -4890,19 +4890,19 @@
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>11</v>
@@ -4910,19 +4910,19 @@
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>11</v>
@@ -4930,19 +4930,19 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>11</v>
@@ -4950,19 +4950,19 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>11</v>
@@ -4970,19 +4970,19 @@
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>11</v>
@@ -4990,19 +4990,19 @@
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>11</v>
@@ -5010,19 +5010,19 @@
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>11</v>
@@ -5030,19 +5030,19 @@
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>11</v>
@@ -5050,19 +5050,19 @@
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>11</v>
@@ -5070,19 +5070,19 @@
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>11</v>
@@ -5090,19 +5090,19 @@
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>11</v>
@@ -5110,19 +5110,19 @@
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -5130,19 +5130,19 @@
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>11</v>
@@ -5150,19 +5150,19 @@
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>11</v>
@@ -5170,19 +5170,19 @@
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>11</v>
@@ -5190,19 +5190,19 @@
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>11</v>
@@ -5210,13 +5210,13 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>9</v>
@@ -5230,19 +5230,19 @@
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>11</v>
@@ -5250,19 +5250,19 @@
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>11</v>
@@ -5270,19 +5270,19 @@
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>11</v>
@@ -5290,19 +5290,19 @@
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>11</v>
@@ -5310,19 +5310,19 @@
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -5330,19 +5330,19 @@
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>11</v>
@@ -5350,19 +5350,19 @@
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>11</v>
@@ -5370,19 +5370,19 @@
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>11</v>
@@ -5390,19 +5390,19 @@
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D89" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -5410,19 +5410,19 @@
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -5430,19 +5430,19 @@
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -5450,19 +5450,19 @@
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>11</v>
@@ -5470,19 +5470,19 @@
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>11</v>
@@ -5490,19 +5490,19 @@
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>11</v>
@@ -5510,19 +5510,19 @@
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>11</v>
@@ -5530,19 +5530,19 @@
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>11</v>
@@ -5550,19 +5550,19 @@
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>11</v>
@@ -5570,19 +5570,19 @@
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>11</v>
@@ -5590,19 +5590,19 @@
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>11</v>
@@ -5610,19 +5610,19 @@
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>11</v>
@@ -5630,19 +5630,19 @@
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>11</v>
@@ -5650,19 +5650,19 @@
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>220</v>
+        <v>23</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -5673,7 +5673,7 @@
         <v>221</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>222</v>
@@ -5693,16 +5693,16 @@
         <v>223</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>224</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -5713,16 +5713,16 @@
         <v>225</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>226</v>
       </c>
       <c r="D105" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>11</v>
@@ -5733,16 +5733,16 @@
         <v>227</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>228</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>11</v>
@@ -5753,7 +5753,7 @@
         <v>229</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>230</v>
@@ -5762,7 +5762,7 @@
         <v>9</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>11</v>
@@ -5773,16 +5773,16 @@
         <v>231</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>232</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>11</v>
@@ -5793,16 +5793,16 @@
         <v>233</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>234</v>
       </c>
       <c r="D109" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>11</v>
@@ -5813,16 +5813,16 @@
         <v>235</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>11</v>
@@ -5833,7 +5833,7 @@
         <v>237</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>238</v>
@@ -5842,7 +5842,7 @@
         <v>9</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>11</v>
@@ -5859,7 +5859,7 @@
         <v>241</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>10</v>
@@ -5879,10 +5879,10 @@
         <v>243</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>11</v>
@@ -5899,10 +5899,10 @@
         <v>245</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>11</v>
@@ -5939,10 +5939,10 @@
         <v>249</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>11</v>
@@ -5959,10 +5959,10 @@
         <v>251</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>11</v>
@@ -5979,10 +5979,10 @@
         <v>253</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>11</v>
@@ -6002,7 +6002,7 @@
         <v>9</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>11</v>
@@ -6019,10 +6019,10 @@
         <v>257</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>11</v>
@@ -6039,10 +6039,10 @@
         <v>259</v>
       </c>
       <c r="D121" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>11</v>
@@ -6059,10 +6059,10 @@
         <v>261</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -6082,7 +6082,7 @@
         <v>9</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -6099,10 +6099,10 @@
         <v>265</v>
       </c>
       <c r="D124" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>11</v>
@@ -6119,10 +6119,10 @@
         <v>267</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>11</v>
@@ -6139,10 +6139,10 @@
         <v>269</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>11</v>
@@ -6162,7 +6162,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>11</v>
@@ -6179,10 +6179,10 @@
         <v>273</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>11</v>
@@ -6199,10 +6199,10 @@
         <v>275</v>
       </c>
       <c r="D129" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E129" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>11</v>
@@ -6219,10 +6219,10 @@
         <v>277</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>11</v>
@@ -6242,7 +6242,7 @@
         <v>9</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>11</v>
@@ -6259,10 +6259,10 @@
         <v>281</v>
       </c>
       <c r="D132" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>11</v>
@@ -6279,7 +6279,7 @@
         <v>283</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>10</v>
@@ -6299,10 +6299,10 @@
         <v>285</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>11</v>
@@ -6322,7 +6322,7 @@
         <v>9</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>11</v>
@@ -6339,10 +6339,10 @@
         <v>289</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>11</v>
@@ -6359,10 +6359,10 @@
         <v>291</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>11</v>
@@ -6379,10 +6379,10 @@
         <v>293</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>11</v>
@@ -6402,7 +6402,7 @@
         <v>9</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>11</v>
@@ -6419,10 +6419,10 @@
         <v>297</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>11</v>
@@ -6439,7 +6439,7 @@
         <v>299</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>10</v>
@@ -6462,7 +6462,7 @@
         <v>9</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>11</v>
@@ -6479,10 +6479,10 @@
         <v>304</v>
       </c>
       <c r="D143" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E143" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>11</v>
@@ -6499,10 +6499,10 @@
         <v>306</v>
       </c>
       <c r="D144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>11</v>
@@ -6519,10 +6519,10 @@
         <v>308</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>11</v>
@@ -6542,7 +6542,7 @@
         <v>9</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>11</v>
@@ -6559,10 +6559,10 @@
         <v>312</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>11</v>
@@ -6579,10 +6579,10 @@
         <v>314</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>11</v>
@@ -6599,10 +6599,10 @@
         <v>316</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>11</v>
@@ -6622,7 +6622,7 @@
         <v>9</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>11</v>
@@ -6639,10 +6639,10 @@
         <v>320</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>11</v>
@@ -6659,10 +6659,10 @@
         <v>322</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>11</v>
@@ -6679,10 +6679,10 @@
         <v>324</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>11</v>
@@ -6702,7 +6702,7 @@
         <v>9</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>11</v>
@@ -6719,10 +6719,10 @@
         <v>328</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>11</v>
@@ -6739,10 +6739,10 @@
         <v>330</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>11</v>
@@ -6759,10 +6759,10 @@
         <v>332</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>11</v>
@@ -6782,7 +6782,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>11</v>
@@ -6799,10 +6799,10 @@
         <v>336</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>11</v>
@@ -6819,10 +6819,10 @@
         <v>338</v>
       </c>
       <c r="D160" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>11</v>
@@ -6839,10 +6839,10 @@
         <v>340</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>11</v>
@@ -6862,7 +6862,7 @@
         <v>9</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>11</v>
@@ -6879,10 +6879,10 @@
         <v>345</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>11</v>
@@ -6899,10 +6899,10 @@
         <v>347</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>11</v>
@@ -6919,7 +6919,7 @@
         <v>349</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>10</v>
@@ -6942,7 +6942,7 @@
         <v>9</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>11</v>
@@ -6959,10 +6959,10 @@
         <v>353</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>11</v>
@@ -6979,10 +6979,10 @@
         <v>355</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>11</v>
@@ -6999,10 +6999,10 @@
         <v>357</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>11</v>
@@ -7022,7 +7022,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>11</v>
@@ -7039,10 +7039,10 @@
         <v>361</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>11</v>
@@ -7059,10 +7059,10 @@
         <v>363</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>11</v>
@@ -7079,10 +7079,10 @@
         <v>365</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>11</v>
@@ -7102,7 +7102,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>11</v>
@@ -7119,10 +7119,10 @@
         <v>369</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>11</v>
@@ -7139,10 +7139,10 @@
         <v>371</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>11</v>
@@ -7159,10 +7159,10 @@
         <v>373</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>11</v>
@@ -7182,7 +7182,7 @@
         <v>9</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>11</v>
@@ -7199,10 +7199,10 @@
         <v>377</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>11</v>
@@ -7219,10 +7219,10 @@
         <v>379</v>
       </c>
       <c r="D180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>11</v>
@@ -7239,10 +7239,10 @@
         <v>381</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>11</v>
@@ -7262,7 +7262,7 @@
         <v>9</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>11</v>
@@ -7279,10 +7279,10 @@
         <v>385</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>11</v>
@@ -7299,10 +7299,10 @@
         <v>387</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>11</v>
@@ -7319,7 +7319,7 @@
         <v>389</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>10</v>
@@ -7342,7 +7342,7 @@
         <v>9</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>11</v>
@@ -7359,7 +7359,7 @@
         <v>393</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>10</v>
@@ -7379,10 +7379,10 @@
         <v>395</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>220</v>
+        <v>23</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>11</v>
@@ -7399,10 +7399,10 @@
         <v>397</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>11</v>
@@ -7422,7 +7422,7 @@
         <v>9</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>11</v>
@@ -7439,10 +7439,10 @@
         <v>401</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>11</v>
@@ -7459,10 +7459,10 @@
         <v>403</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>11</v>
@@ -7479,10 +7479,10 @@
         <v>405</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>11</v>
@@ -7502,7 +7502,7 @@
         <v>9</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>11</v>
@@ -7519,10 +7519,10 @@
         <v>409</v>
       </c>
       <c r="D195" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E195" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E195" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>11</v>
@@ -7539,10 +7539,10 @@
         <v>411</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>11</v>
@@ -7559,10 +7559,10 @@
         <v>413</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>11</v>
@@ -7599,10 +7599,10 @@
         <v>417</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>11</v>
@@ -7619,10 +7619,10 @@
         <v>419</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>11</v>
@@ -7639,10 +7639,10 @@
         <v>421</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>11</v>
@@ -7662,7 +7662,7 @@
         <v>9</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>11</v>
@@ -7682,7 +7682,7 @@
         <v>9</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>11</v>
@@ -7699,10 +7699,10 @@
         <v>428</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>11</v>
@@ -7719,10 +7719,10 @@
         <v>430</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>11</v>
@@ -7742,7 +7742,7 @@
         <v>9</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>11</v>
@@ -7762,7 +7762,7 @@
         <v>9</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>11</v>
@@ -7779,10 +7779,10 @@
         <v>436</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>11</v>
@@ -7799,10 +7799,10 @@
         <v>438</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>11</v>
@@ -7822,7 +7822,7 @@
         <v>9</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>11</v>
@@ -7842,7 +7842,7 @@
         <v>9</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>11</v>
@@ -7859,10 +7859,10 @@
         <v>444</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>11</v>
@@ -7879,10 +7879,10 @@
         <v>446</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>11</v>
@@ -7902,7 +7902,7 @@
         <v>9</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>11</v>
@@ -7922,7 +7922,7 @@
         <v>9</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>11</v>
@@ -7939,10 +7939,10 @@
         <v>452</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>11</v>
@@ -7959,10 +7959,10 @@
         <v>454</v>
       </c>
       <c r="D217" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E217" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E217" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>11</v>
@@ -7982,7 +7982,7 @@
         <v>9</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>11</v>
@@ -8002,7 +8002,7 @@
         <v>9</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>11</v>
@@ -8019,10 +8019,10 @@
         <v>460</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>11</v>
@@ -8039,10 +8039,10 @@
         <v>462</v>
       </c>
       <c r="D221" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E221" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E221" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>11</v>
@@ -8082,7 +8082,7 @@
         <v>9</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>11</v>
@@ -8099,10 +8099,10 @@
         <v>468</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>11</v>
@@ -8119,10 +8119,10 @@
         <v>470</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>11</v>
@@ -8142,7 +8142,7 @@
         <v>9</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>11</v>
@@ -8162,7 +8162,7 @@
         <v>9</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>11</v>
@@ -8179,10 +8179,10 @@
         <v>476</v>
       </c>
       <c r="D228" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E228" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>11</v>
@@ -8199,10 +8199,10 @@
         <v>478</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>11</v>
@@ -8222,7 +8222,7 @@
         <v>9</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>11</v>
@@ -8259,10 +8259,10 @@
         <v>484</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>11</v>
@@ -8279,10 +8279,10 @@
         <v>486</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>11</v>
@@ -8302,7 +8302,7 @@
         <v>9</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>11</v>
@@ -8322,7 +8322,7 @@
         <v>9</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>11</v>
@@ -8339,10 +8339,10 @@
         <v>492</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>220</v>
+        <v>10</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>11</v>
@@ -8359,10 +8359,10 @@
         <v>494</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>11</v>
@@ -8382,7 +8382,7 @@
         <v>9</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>11</v>
@@ -8402,7 +8402,7 @@
         <v>9</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>11</v>
@@ -8419,10 +8419,10 @@
         <v>500</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>11</v>
@@ -8439,10 +8439,10 @@
         <v>502</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>11</v>
@@ -8459,10 +8459,10 @@
         <v>505</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>11</v>
@@ -8479,10 +8479,10 @@
         <v>507</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>11</v>
@@ -8502,7 +8502,7 @@
         <v>9</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>11</v>
@@ -8519,10 +8519,10 @@
         <v>511</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>11</v>
@@ -8539,10 +8539,10 @@
         <v>513</v>
       </c>
       <c r="D246" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>11</v>
@@ -8559,10 +8559,10 @@
         <v>515</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E247" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>11</v>
@@ -8582,7 +8582,7 @@
         <v>9</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>11</v>
@@ -8599,10 +8599,10 @@
         <v>519</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E249" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>11</v>
@@ -8619,10 +8619,10 @@
         <v>521</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>11</v>
@@ -8639,10 +8639,10 @@
         <v>523</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>11</v>
@@ -8662,7 +8662,7 @@
         <v>9</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>11</v>
@@ -8679,7 +8679,7 @@
         <v>527</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E253" s="4" t="s">
         <v>10</v>
@@ -8699,10 +8699,10 @@
         <v>529</v>
       </c>
       <c r="D254" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>11</v>
@@ -8719,10 +8719,10 @@
         <v>531</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>11</v>
@@ -8742,7 +8742,7 @@
         <v>9</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>11</v>
@@ -8759,10 +8759,10 @@
         <v>535</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>11</v>
@@ -8779,10 +8779,10 @@
         <v>537</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>11</v>
@@ -8799,10 +8799,10 @@
         <v>539</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E259" s="4" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>11</v>
@@ -8822,7 +8822,7 @@
         <v>9</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>11</v>
@@ -8839,10 +8839,10 @@
         <v>543</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E261" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>11</v>
@@ -8859,10 +8859,10 @@
         <v>546</v>
       </c>
       <c r="D262" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E262" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>11</v>
@@ -8879,10 +8879,10 @@
         <v>548</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>11</v>
@@ -8899,10 +8899,10 @@
         <v>550</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>11</v>
@@ -8919,10 +8919,10 @@
         <v>552</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E265" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>11</v>
@@ -8939,10 +8939,10 @@
         <v>554</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>11</v>
@@ -8959,10 +8959,10 @@
         <v>556</v>
       </c>
       <c r="D267" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E267" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E267" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>11</v>
@@ -8979,10 +8979,10 @@
         <v>558</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>11</v>
@@ -8999,7 +8999,7 @@
         <v>560</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E269" s="4" t="s">
         <v>10</v>
@@ -9019,10 +9019,10 @@
         <v>562</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>11</v>
@@ -9039,10 +9039,10 @@
         <v>564</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E271" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>11</v>
@@ -9059,10 +9059,10 @@
         <v>566</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>11</v>
@@ -9079,10 +9079,10 @@
         <v>568</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E273" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>11</v>
@@ -9099,10 +9099,10 @@
         <v>570</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>11</v>
@@ -9119,10 +9119,10 @@
         <v>572</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E275" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>11</v>
@@ -9139,10 +9139,10 @@
         <v>574</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>11</v>
@@ -9159,10 +9159,10 @@
         <v>576</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E277" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>11</v>
@@ -9179,10 +9179,10 @@
         <v>578</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>11</v>
@@ -9199,10 +9199,10 @@
         <v>580</v>
       </c>
       <c r="D279" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E279" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E279" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>11</v>
@@ -9219,10 +9219,10 @@
         <v>582</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>11</v>
@@ -9239,10 +9239,10 @@
         <v>584</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E281" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>11</v>
@@ -9262,7 +9262,7 @@
         <v>9</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>11</v>
@@ -9279,10 +9279,10 @@
         <v>589</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E283" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>11</v>
@@ -9299,10 +9299,10 @@
         <v>591</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>11</v>
@@ -9319,10 +9319,10 @@
         <v>593</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E285" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>11</v>
@@ -9342,7 +9342,7 @@
         <v>9</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>11</v>
@@ -9359,10 +9359,10 @@
         <v>597</v>
       </c>
       <c r="D287" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E287" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E287" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>11</v>
@@ -9379,7 +9379,7 @@
         <v>599</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>10</v>
@@ -9399,10 +9399,10 @@
         <v>601</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E289" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>11</v>
@@ -9439,10 +9439,10 @@
         <v>605</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E291" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>11</v>
@@ -9459,10 +9459,10 @@
         <v>607</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>11</v>
@@ -9479,10 +9479,10 @@
         <v>609</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E293" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>11</v>
@@ -9502,7 +9502,7 @@
         <v>9</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>11</v>
@@ -9519,10 +9519,10 @@
         <v>613</v>
       </c>
       <c r="D295" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E295" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E295" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>11</v>
@@ -9539,10 +9539,10 @@
         <v>615</v>
       </c>
       <c r="D296" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E296" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>11</v>
@@ -9559,10 +9559,10 @@
         <v>617</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E297" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>11</v>
@@ -9582,7 +9582,7 @@
         <v>9</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>11</v>
@@ -9599,10 +9599,10 @@
         <v>621</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E299" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>11</v>
@@ -9619,10 +9619,10 @@
         <v>623</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>11</v>
@@ -9639,10 +9639,10 @@
         <v>625</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E301" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>11</v>
@@ -9662,7 +9662,7 @@
         <v>9</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>11</v>
@@ -9679,10 +9679,10 @@
         <v>629</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E303" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>11</v>
@@ -9699,10 +9699,10 @@
         <v>631</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>11</v>
@@ -9719,10 +9719,10 @@
         <v>633</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E305" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>11</v>
@@ -9759,10 +9759,10 @@
         <v>637</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E307" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>11</v>
@@ -9779,10 +9779,10 @@
         <v>639</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>11</v>
@@ -9799,10 +9799,10 @@
         <v>641</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E309" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>11</v>
@@ -9822,7 +9822,7 @@
         <v>9</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>11</v>
@@ -9839,10 +9839,10 @@
         <v>645</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E311" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>11</v>
@@ -9859,10 +9859,10 @@
         <v>647</v>
       </c>
       <c r="D312" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E312" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>11</v>
@@ -9879,10 +9879,10 @@
         <v>649</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E313" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>11</v>
@@ -9902,7 +9902,7 @@
         <v>9</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>11</v>
@@ -9919,10 +9919,10 @@
         <v>653</v>
       </c>
       <c r="D315" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E315" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E315" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>11</v>
@@ -9939,10 +9939,10 @@
         <v>655</v>
       </c>
       <c r="D316" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E316" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>11</v>
@@ -9959,10 +9959,10 @@
         <v>657</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E317" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>11</v>
@@ -9982,7 +9982,7 @@
         <v>9</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>11</v>
@@ -9999,10 +9999,10 @@
         <v>661</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E319" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>11</v>
@@ -10019,10 +10019,10 @@
         <v>663</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>11</v>
@@ -10039,10 +10039,10 @@
         <v>665</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E321" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>11</v>
@@ -10059,10 +10059,10 @@
         <v>668</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>11</v>
@@ -10079,10 +10079,10 @@
         <v>670</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E323" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>11</v>
@@ -10102,7 +10102,7 @@
         <v>9</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>11</v>
@@ -10119,10 +10119,10 @@
         <v>674</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E325" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>11</v>
@@ -10139,10 +10139,10 @@
         <v>676</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>11</v>
@@ -10159,7 +10159,7 @@
         <v>678</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E327" s="4" t="s">
         <v>10</v>
@@ -10182,7 +10182,7 @@
         <v>9</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>11</v>
@@ -10199,7 +10199,7 @@
         <v>682</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E329" s="4" t="s">
         <v>10</v>
@@ -10219,10 +10219,10 @@
         <v>684</v>
       </c>
       <c r="D330" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E330" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E330" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>11</v>
@@ -10239,10 +10239,10 @@
         <v>686</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E331" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>11</v>
@@ -10262,7 +10262,7 @@
         <v>9</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>11</v>
@@ -10279,10 +10279,10 @@
         <v>690</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E333" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>11</v>
@@ -10299,10 +10299,10 @@
         <v>692</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>11</v>
@@ -10319,10 +10319,10 @@
         <v>694</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E335" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>11</v>
@@ -10342,7 +10342,7 @@
         <v>9</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>11</v>
@@ -10359,10 +10359,10 @@
         <v>698</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E337" s="4" t="s">
-        <v>220</v>
+        <v>17</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>11</v>
@@ -10379,10 +10379,10 @@
         <v>700</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>11</v>
@@ -10399,10 +10399,10 @@
         <v>702</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E339" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>11</v>
@@ -10439,10 +10439,10 @@
         <v>706</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E341" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>11</v>
@@ -10462,7 +10462,7 @@
         <v>9</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>11</v>
@@ -10482,7 +10482,7 @@
         <v>9</v>
       </c>
       <c r="E343" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>11</v>
@@ -10499,10 +10499,10 @@
         <v>713</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>11</v>
@@ -10519,10 +10519,10 @@
         <v>715</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E345" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>11</v>
@@ -10562,7 +10562,7 @@
         <v>9</v>
       </c>
       <c r="E347" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>11</v>
@@ -10579,10 +10579,10 @@
         <v>721</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>11</v>
@@ -10599,10 +10599,10 @@
         <v>723</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E349" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>11</v>
@@ -10622,7 +10622,7 @@
         <v>9</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>11</v>
@@ -10642,7 +10642,7 @@
         <v>9</v>
       </c>
       <c r="E351" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>11</v>
@@ -10659,10 +10659,10 @@
         <v>729</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>11</v>
@@ -10679,10 +10679,10 @@
         <v>731</v>
       </c>
       <c r="D353" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E353" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E353" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>11</v>
@@ -10702,7 +10702,7 @@
         <v>9</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>11</v>
@@ -10722,7 +10722,7 @@
         <v>9</v>
       </c>
       <c r="E355" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>11</v>
@@ -10739,10 +10739,10 @@
         <v>737</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>11</v>
@@ -10759,10 +10759,10 @@
         <v>739</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E357" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>11</v>
@@ -10782,7 +10782,7 @@
         <v>9</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>11</v>
@@ -10802,7 +10802,7 @@
         <v>9</v>
       </c>
       <c r="E359" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>11</v>
@@ -10819,10 +10819,10 @@
         <v>745</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>11</v>
@@ -10839,10 +10839,10 @@
         <v>747</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E361" s="4" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>11</v>
@@ -10859,10 +10859,10 @@
         <v>750</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>11</v>
@@ -10879,10 +10879,10 @@
         <v>752</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E363" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>11</v>
@@ -10902,7 +10902,7 @@
         <v>9</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>11</v>
@@ -10919,10 +10919,10 @@
         <v>756</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E365" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>11</v>
@@ -10939,10 +10939,10 @@
         <v>758</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>11</v>
@@ -10959,10 +10959,10 @@
         <v>760</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E367" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>11</v>
@@ -10982,7 +10982,7 @@
         <v>9</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>11</v>
@@ -10999,10 +10999,10 @@
         <v>764</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E369" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>11</v>
@@ -11019,10 +11019,10 @@
         <v>766</v>
       </c>
       <c r="D370" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E370" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E370" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>11</v>
@@ -11039,10 +11039,10 @@
         <v>768</v>
       </c>
       <c r="D371" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E371" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E371" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>11</v>
@@ -11062,7 +11062,7 @@
         <v>9</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>11</v>
@@ -11079,10 +11079,10 @@
         <v>772</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E373" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>11</v>
@@ -11099,10 +11099,10 @@
         <v>774</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>220</v>
+        <v>10</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>11</v>
@@ -11119,10 +11119,10 @@
         <v>776</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E375" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>11</v>
@@ -11142,7 +11142,7 @@
         <v>9</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>11</v>
@@ -11159,10 +11159,10 @@
         <v>780</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E377" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>11</v>
@@ -11179,10 +11179,10 @@
         <v>782</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>11</v>
@@ -11199,10 +11199,10 @@
         <v>784</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E379" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>11</v>
@@ -11222,7 +11222,7 @@
         <v>9</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>11</v>
@@ -11239,10 +11239,10 @@
         <v>788</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E381" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>11</v>
@@ -11259,10 +11259,10 @@
         <v>791</v>
       </c>
       <c r="D382" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E382" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E382" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>11</v>
@@ -11279,10 +11279,10 @@
         <v>793</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E383" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>11</v>
@@ -11302,7 +11302,7 @@
         <v>9</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>11</v>
@@ -11319,7 +11319,7 @@
         <v>797</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E385" s="4" t="s">
         <v>10</v>
@@ -11339,10 +11339,10 @@
         <v>799</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>11</v>
@@ -11359,10 +11359,10 @@
         <v>801</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E387" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>11</v>
@@ -11382,7 +11382,7 @@
         <v>9</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>11</v>
@@ -11399,7 +11399,7 @@
         <v>805</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E389" s="4" t="s">
         <v>10</v>
@@ -11419,10 +11419,10 @@
         <v>807</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>11</v>
@@ -11439,10 +11439,10 @@
         <v>809</v>
       </c>
       <c r="D391" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E391" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E391" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>11</v>
@@ -11462,7 +11462,7 @@
         <v>9</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>11</v>
@@ -11479,10 +11479,10 @@
         <v>813</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E393" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>11</v>
@@ -11499,10 +11499,10 @@
         <v>815</v>
       </c>
       <c r="D394" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E394" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E394" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>11</v>
@@ -11519,10 +11519,10 @@
         <v>817</v>
       </c>
       <c r="D395" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E395" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E395" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>11</v>
@@ -11542,7 +11542,7 @@
         <v>9</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>11</v>
@@ -11559,10 +11559,10 @@
         <v>821</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E397" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>11</v>
@@ -11579,10 +11579,10 @@
         <v>823</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>11</v>
@@ -11599,10 +11599,10 @@
         <v>825</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E399" s="4" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>11</v>
@@ -11639,10 +11639,10 @@
         <v>829</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>11</v>
@@ -11662,7 +11662,7 @@
         <v>9</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F402" s="3" t="s">
         <v>11</v>
@@ -11679,10 +11679,10 @@
         <v>834</v>
       </c>
       <c r="D403" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E403" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E403" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="F403" s="3" t="s">
         <v>11</v>
@@ -11699,10 +11699,10 @@
         <v>836</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>11</v>
@@ -11719,10 +11719,10 @@
         <v>838</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E405" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>11</v>
@@ -11742,7 +11742,7 @@
         <v>9</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F406" s="3" t="s">
         <v>11</v>
@@ -11759,10 +11759,10 @@
         <v>842</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E407" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F407" s="3" t="s">
         <v>11</v>
@@ -11779,10 +11779,10 @@
         <v>844</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F408" s="3" t="s">
         <v>11</v>
@@ -11799,10 +11799,10 @@
         <v>846</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F409" s="3" t="s">
         <v>11</v>
@@ -11822,7 +11822,7 @@
         <v>9</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F410" s="3" t="s">
         <v>11</v>
@@ -11839,7 +11839,7 @@
         <v>850</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E411" s="4" t="s">
         <v>10</v>
@@ -11859,10 +11859,10 @@
         <v>853</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>11</v>
@@ -11879,10 +11879,10 @@
         <v>855</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E413" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F413" s="3" t="s">
         <v>11</v>
@@ -11899,10 +11899,10 @@
         <v>857</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>11</v>
@@ -11919,10 +11919,10 @@
         <v>859</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E415" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F415" s="3" t="s">
         <v>11</v>
@@ -11939,10 +11939,10 @@
         <v>861</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F416" s="3" t="s">
         <v>11</v>
@@ -11959,10 +11959,10 @@
         <v>863</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E417" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F417" s="3" t="s">
         <v>11</v>
@@ -11979,10 +11979,10 @@
         <v>865</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F418" s="3" t="s">
         <v>11</v>
@@ -11999,10 +11999,10 @@
         <v>867</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E419" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F419" s="3" t="s">
         <v>11</v>
@@ -12019,10 +12019,10 @@
         <v>869</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F420" s="3" t="s">
         <v>11</v>
@@ -12039,10 +12039,10 @@
         <v>871</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E421" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F421" s="3" t="s">
         <v>11</v>
@@ -12059,10 +12059,10 @@
         <v>873</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F422" s="3" t="s">
         <v>11</v>
@@ -12079,10 +12079,10 @@
         <v>875</v>
       </c>
       <c r="D423" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E423" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E423" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F423" s="3" t="s">
         <v>11</v>
@@ -12099,10 +12099,10 @@
         <v>877</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F424" s="3" t="s">
         <v>11</v>
@@ -12119,10 +12119,10 @@
         <v>879</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E425" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>11</v>
@@ -12139,10 +12139,10 @@
         <v>881</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>11</v>
@@ -12159,7 +12159,7 @@
         <v>883</v>
       </c>
       <c r="D427" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E427" s="4" t="s">
         <v>10</v>
@@ -12179,10 +12179,10 @@
         <v>885</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>11</v>
@@ -12199,10 +12199,10 @@
         <v>887</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E429" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>11</v>
@@ -12219,10 +12219,10 @@
         <v>889</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>11</v>
@@ -12239,10 +12239,10 @@
         <v>891</v>
       </c>
       <c r="D431" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E431" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E431" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>11</v>
@@ -12259,10 +12259,10 @@
         <v>894</v>
       </c>
       <c r="D432" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E432" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E432" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>11</v>
@@ -12279,10 +12279,10 @@
         <v>896</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E433" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>11</v>
@@ -12299,10 +12299,10 @@
         <v>898</v>
       </c>
       <c r="D434" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E434" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E434" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>11</v>
@@ -12319,10 +12319,10 @@
         <v>900</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E435" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>11</v>
@@ -12339,10 +12339,10 @@
         <v>902</v>
       </c>
       <c r="D436" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E436" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E436" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F436" s="3" t="s">
         <v>11</v>
@@ -12359,10 +12359,10 @@
         <v>904</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E437" s="4" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="F437" s="3" t="s">
         <v>11</v>
@@ -12379,10 +12379,10 @@
         <v>906</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F438" s="3" t="s">
         <v>11</v>
@@ -12399,10 +12399,10 @@
         <v>908</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E439" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F439" s="3" t="s">
         <v>11</v>
@@ -12419,10 +12419,10 @@
         <v>910</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F440" s="3" t="s">
         <v>11</v>
@@ -12439,10 +12439,10 @@
         <v>912</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E441" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F441" s="3" t="s">
         <v>11</v>
@@ -12459,10 +12459,10 @@
         <v>915</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F442" s="3" t="s">
         <v>11</v>
@@ -12482,7 +12482,7 @@
         <v>9</v>
       </c>
       <c r="E443" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F443" s="3" t="s">
         <v>11</v>
@@ -12499,10 +12499,10 @@
         <v>919</v>
       </c>
       <c r="D444" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E444" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E444" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F444" s="3" t="s">
         <v>11</v>
@@ -12519,10 +12519,10 @@
         <v>921</v>
       </c>
       <c r="D445" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E445" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F445" s="3" t="s">
         <v>11</v>
@@ -12539,10 +12539,10 @@
         <v>923</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F446" s="3" t="s">
         <v>11</v>
@@ -12562,7 +12562,7 @@
         <v>9</v>
       </c>
       <c r="E447" s="4" t="s">
-        <v>220</v>
+        <v>23</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>11</v>
@@ -12579,10 +12579,10 @@
         <v>927</v>
       </c>
       <c r="D448" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E448" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E448" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>11</v>
@@ -12599,10 +12599,10 @@
         <v>929</v>
       </c>
       <c r="D449" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E449" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>11</v>
@@ -12619,10 +12619,10 @@
         <v>931</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F450" s="3" t="s">
         <v>11</v>
@@ -12642,7 +12642,7 @@
         <v>9</v>
       </c>
       <c r="E451" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F451" s="3" t="s">
         <v>11</v>
@@ -12659,10 +12659,10 @@
         <v>935</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F452" s="3" t="s">
         <v>11</v>
@@ -12679,10 +12679,10 @@
         <v>937</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E453" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>11</v>
@@ -12699,10 +12699,10 @@
         <v>939</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F454" s="3" t="s">
         <v>11</v>
@@ -12722,7 +12722,7 @@
         <v>9</v>
       </c>
       <c r="E455" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F455" s="3" t="s">
         <v>11</v>
@@ -12739,10 +12739,10 @@
         <v>943</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F456" s="3" t="s">
         <v>11</v>
@@ -12759,10 +12759,10 @@
         <v>945</v>
       </c>
       <c r="D457" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E457" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F457" s="3" t="s">
         <v>11</v>
@@ -12779,10 +12779,10 @@
         <v>947</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F458" s="3" t="s">
         <v>11</v>
@@ -12802,7 +12802,7 @@
         <v>9</v>
       </c>
       <c r="E459" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F459" s="3" t="s">
         <v>11</v>
@@ -12819,10 +12819,10 @@
         <v>951</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F460" s="3" t="s">
         <v>11</v>
@@ -12839,10 +12839,10 @@
         <v>953</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E461" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>11</v>
@@ -12862,7 +12862,7 @@
         <v>9</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>11</v>
@@ -12882,7 +12882,7 @@
         <v>9</v>
       </c>
       <c r="E463" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F463" s="3" t="s">
         <v>11</v>
@@ -12899,10 +12899,10 @@
         <v>960</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F464" s="3" t="s">
         <v>11</v>
@@ -12919,7 +12919,7 @@
         <v>962</v>
       </c>
       <c r="D465" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E465" s="4" t="s">
         <v>10</v>
@@ -12942,7 +12942,7 @@
         <v>9</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F466" s="3" t="s">
         <v>11</v>
@@ -12962,7 +12962,7 @@
         <v>9</v>
       </c>
       <c r="E467" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F467" s="3" t="s">
         <v>11</v>
@@ -12979,10 +12979,10 @@
         <v>968</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>11</v>
@@ -12999,10 +12999,10 @@
         <v>970</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E469" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F469" s="3" t="s">
         <v>11</v>
@@ -13022,7 +13022,7 @@
         <v>9</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F470" s="3" t="s">
         <v>11</v>
@@ -13042,7 +13042,7 @@
         <v>9</v>
       </c>
       <c r="E471" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F471" s="3" t="s">
         <v>11</v>
@@ -13059,7 +13059,7 @@
         <v>976</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>10</v>
@@ -13079,10 +13079,10 @@
         <v>978</v>
       </c>
       <c r="D473" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E473" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F473" s="3" t="s">
         <v>11</v>
@@ -13102,7 +13102,7 @@
         <v>9</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>11</v>
@@ -13122,7 +13122,7 @@
         <v>9</v>
       </c>
       <c r="E475" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>11</v>
@@ -13139,10 +13139,10 @@
         <v>984</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F476" s="3" t="s">
         <v>11</v>
@@ -13159,10 +13159,10 @@
         <v>986</v>
       </c>
       <c r="D477" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E477" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F477" s="3" t="s">
         <v>11</v>
@@ -13182,7 +13182,7 @@
         <v>9</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F478" s="3" t="s">
         <v>11</v>
@@ -13219,10 +13219,10 @@
         <v>992</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>11</v>
@@ -13239,10 +13239,10 @@
         <v>994</v>
       </c>
       <c r="D481" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E481" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E481" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F481" s="3" t="s">
         <v>11</v>
@@ -13262,7 +13262,7 @@
         <v>9</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F482" s="3" t="s">
         <v>11</v>
@@ -13282,7 +13282,7 @@
         <v>9</v>
       </c>
       <c r="E483" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F483" s="3" t="s">
         <v>11</v>
@@ -13299,10 +13299,10 @@
         <v>1000</v>
       </c>
       <c r="D484" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E484" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E484" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F484" s="3" t="s">
         <v>11</v>
@@ -13319,10 +13319,10 @@
         <v>1002</v>
       </c>
       <c r="D485" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E485" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F485" s="3" t="s">
         <v>11</v>
@@ -13342,7 +13342,7 @@
         <v>9</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F486" s="3" t="s">
         <v>11</v>
@@ -13362,7 +13362,7 @@
         <v>9</v>
       </c>
       <c r="E487" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F487" s="3" t="s">
         <v>11</v>
@@ -13379,10 +13379,10 @@
         <v>1008</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F488" s="3" t="s">
         <v>11</v>
@@ -13399,10 +13399,10 @@
         <v>1010</v>
       </c>
       <c r="D489" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E489" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F489" s="3" t="s">
         <v>11</v>
@@ -13422,7 +13422,7 @@
         <v>9</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F490" s="3" t="s">
         <v>11</v>
@@ -13442,7 +13442,7 @@
         <v>9</v>
       </c>
       <c r="E491" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F491" s="3" t="s">
         <v>11</v>
@@ -13459,10 +13459,10 @@
         <v>1016</v>
       </c>
       <c r="D492" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E492" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E492" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="F492" s="3" t="s">
         <v>11</v>
@@ -13479,10 +13479,10 @@
         <v>1018</v>
       </c>
       <c r="D493" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E493" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E493" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F493" s="3" t="s">
         <v>11</v>
@@ -13502,7 +13502,7 @@
         <v>9</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F494" s="3" t="s">
         <v>11</v>
@@ -13522,7 +13522,7 @@
         <v>9</v>
       </c>
       <c r="E495" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>11</v>
@@ -13539,10 +13539,10 @@
         <v>1024</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F496" s="3" t="s">
         <v>11</v>
@@ -13559,10 +13559,10 @@
         <v>1026</v>
       </c>
       <c r="D497" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E497" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E497" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F497" s="3" t="s">
         <v>11</v>
@@ -13582,7 +13582,7 @@
         <v>9</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F498" s="3" t="s">
         <v>11</v>
@@ -13619,10 +13619,10 @@
         <v>1032</v>
       </c>
       <c r="D500" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F500" s="3" t="s">
         <v>11</v>
@@ -13639,10 +13639,10 @@
         <v>1034</v>
       </c>
       <c r="D501" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E501" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F501" s="3" t="s">
         <v>11</v>
@@ -13662,7 +13662,7 @@
         <v>9</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F502" s="3" t="s">
         <v>11</v>
@@ -13682,7 +13682,7 @@
         <v>9</v>
       </c>
       <c r="E503" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F503" s="3" t="s">
         <v>11</v>
@@ -13699,10 +13699,10 @@
         <v>1040</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F504" s="3" t="s">
         <v>11</v>
@@ -13719,10 +13719,10 @@
         <v>1042</v>
       </c>
       <c r="D505" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E505" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F505" s="3" t="s">
         <v>11</v>
@@ -13742,7 +13742,7 @@
         <v>9</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F506" s="3" t="s">
         <v>11</v>
@@ -13762,7 +13762,7 @@
         <v>9</v>
       </c>
       <c r="E507" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F507" s="3" t="s">
         <v>11</v>
@@ -13779,10 +13779,10 @@
         <v>1048</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F508" s="3" t="s">
         <v>11</v>
@@ -13799,10 +13799,10 @@
         <v>1050</v>
       </c>
       <c r="D509" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E509" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F509" s="3" t="s">
         <v>11</v>
@@ -13822,7 +13822,7 @@
         <v>9</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F510" s="3" t="s">
         <v>11</v>
@@ -13842,7 +13842,7 @@
         <v>9</v>
       </c>
       <c r="E511" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F511" s="3" t="s">
         <v>11</v>
